--- a/app/zen_rules/bank_Company_Organization_Eligibility_Matrix.xlsx
+++ b/app/zen_rules/bank_Company_Organization_Eligibility_Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="57">
   <si>
     <t>Bank Name</t>
   </si>
@@ -64,16 +64,13 @@
     <t>Existing Car Loan</t>
   </si>
   <si>
-    <t>SE Current ITR</t>
-  </si>
-  <si>
-    <t>SE Previous ITR</t>
-  </si>
-  <si>
-    <t>Self Employed</t>
-  </si>
-  <si>
-    <t>Self Employed ITR Filed</t>
+    <t>Current ITR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Previous ITR</t>
+  </si>
+  <si>
+    <t>ITR Filed</t>
   </si>
   <si>
     <t>ITR Not Filed</t>
@@ -534,7 +531,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -553,16 +550,15 @@
     <col min="14" max="14" style="2" width="29.433571428571426" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="2" width="22.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="2" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="2" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="2" width="25.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="2" width="25.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="2" width="26.005" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -641,648 +637,621 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="V3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="S5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/app/zen_rules/bank_Company_Organization_Eligibility_Matrix.xlsx
+++ b/app/zen_rules/bank_Company_Organization_Eligibility_Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="58">
   <si>
     <t>Bank Name</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>&gt;= 726</t>
+  </si>
+  <si>
+    <t>condition</t>
   </si>
   <si>
     <t>Current + Prev &gt;= 600000</t>
@@ -919,10 +922,10 @@
         <v>28</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>29</v>
@@ -948,13 +951,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>28</v>
@@ -978,7 +981,7 @@
         <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>31</v>
@@ -1025,10 +1028,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
@@ -1102,10 +1105,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
@@ -1179,10 +1182,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>27</v>
